--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week06_05Oct.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week06_05Oct.xlsx
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>TA runs the hoop sort. Teacher keeps the plant on the desk all three nutrition weeks as the constant reference. LOOP [Feedback Policy]: Voice = sort/point/say [VF, ?] → Audience: say who must eat; [R] once received → EVIDENCE: hoop-sort photo, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+          <t>TA runs the hoop sort. Teacher keeps the plant on the desk all three nutrition weeks as the constant reference. LOOP [Feedback Policy]: Voice = sort/point/say [VF, ?] → Audience: say who must eat; [R] once received → EVIDENCE: hoop-sort photo, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
         </is>
       </c>
       <c r="J12" s="56" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="I13" s="58" t="inlineStr">
         <is>
-          <t>TA walks the barometer alongside and models the stem first.  LOOP [Feedback Policy]: Voice = walk/stem/make [VF] → Audience: name the respectful move back; [R] when a stem is used for real → EVIDENCE: poster/video, same day [E: BV mutual respect — daily EFL; banks AQA UAS].</t>
+          <t>TA walks the barometer alongside and models the stem first.  LOOP [Feedback Policy]: Voice = walk/stem/make [VF] → Audience: name the respectful move back; [R] when a stem is used for real → EVIDENCE: poster/video, same day [E: BV mutual respect — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J13" s="58" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>TA referees placements and captures the sames said aloud.  LOOP [Feedback Policy]: Voice = place/say a same [VF, ?] → Audience: name the comparison back; [R] once received → EVIDENCE: grid photo + display, same day [E: cultural — daily EFL].</t>
+          <t>TA referees placements and captures the sames said aloud.  LOOP [Feedback Policy]: Voice = place/say a same [VF, ?] → Audience: name the comparison back; [R] once received → EVIDENCE: grid photo + display, same day [E: cultural — daily evidence platform].</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>TA chants the frame and scribes box captions.  LOOP [Feedback Policy]: Voice = order/stick/say box one [VF, ?] → Audience: name the story shape back; [R] once received → EVIDENCE: storyboard photo, same day [E: humanities — daily EFL; banks AQA UAS].</t>
+          <t>TA chants the frame and scribes box captions.  LOOP [Feedback Policy]: Voice = order/stick/say box one [VF, ?] → Audience: name the story shape back; [R] once received → EVIDENCE: storyboard photo, same day [E: humanities — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
